--- a/research/traditional_assets/database/data/kenya/kenya_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_electrical_equipment.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.135</v>
+        <v>-0.127</v>
       </c>
       <c r="G2">
-        <v>-0.04187878787878788</v>
+        <v>0.005092024539877301</v>
       </c>
       <c r="H2">
-        <v>-0.04187878787878788</v>
+        <v>0.005092024539877301</v>
       </c>
       <c r="I2">
-        <v>-0.1442424242424242</v>
+        <v>-0.09509202453987729</v>
       </c>
       <c r="J2">
-        <v>-0.1442424242424242</v>
+        <v>-0.09509202453987729</v>
       </c>
       <c r="K2">
-        <v>-4.98</v>
+        <v>-2.35</v>
       </c>
       <c r="L2">
-        <v>-0.3018181818181818</v>
+        <v>-0.1441717791411043</v>
       </c>
       <c r="M2">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="N2">
-        <v>0.005223880597014926</v>
+        <v>0.005813953488372093</v>
       </c>
       <c r="O2">
-        <v>-0.002811244979919678</v>
+        <v>-0.00425531914893617</v>
       </c>
       <c r="P2">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="Q2">
-        <v>0.005223880597014926</v>
+        <v>0.005813953488372093</v>
       </c>
       <c r="R2">
-        <v>-0.002811244979919678</v>
+        <v>-0.00425531914893617</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,52 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.6492537313432836</v>
-      </c>
-      <c r="W2">
-        <v>-0.2721311475409836</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.812851097113492</v>
-      </c>
-      <c r="Y2">
-        <v>-1.084982244654476</v>
-      </c>
-      <c r="Z2">
-        <v>0.3791360294117647</v>
-      </c>
-      <c r="AA2">
-        <v>-0.05468749999999999</v>
+        <v>0.208997860567781</v>
       </c>
       <c r="AB2">
-        <v>0.1202382466294079</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1749257466294079</v>
+        <v>0.208997860567781</v>
       </c>
       <c r="AD2">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>24.36</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.9068797776233496</v>
-      </c>
-      <c r="AI2">
-        <v>0.6726804123711341</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.900887573964497</v>
-      </c>
-      <c r="AK2">
-        <v>0.6573124662709121</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AM2">
-        <v>3.08</v>
+        <v>2.397</v>
       </c>
       <c r="AN2">
-        <v>-37.7713458755427</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-0.7727272727272727</v>
+        <v>-0.5363321799307958</v>
       </c>
       <c r="AP2">
-        <v>-35.25325615050652</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-0.7727272727272727</v>
+        <v>-0.6466416353775553</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +698,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.135</v>
+        <v>-0.127</v>
       </c>
       <c r="G3">
-        <v>-0.04187878787878788</v>
+        <v>0.005092024539877301</v>
       </c>
       <c r="H3">
-        <v>-0.04187878787878788</v>
+        <v>0.005092024539877301</v>
       </c>
       <c r="I3">
-        <v>-0.1442424242424242</v>
+        <v>-0.09509202453987729</v>
       </c>
       <c r="J3">
-        <v>-0.1442424242424242</v>
+        <v>-0.09509202453987729</v>
       </c>
       <c r="K3">
-        <v>-4.98</v>
+        <v>-2.35</v>
       </c>
       <c r="L3">
-        <v>-0.3018181818181818</v>
+        <v>-0.1441717791411043</v>
       </c>
       <c r="M3">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="N3">
-        <v>0.005223880597014926</v>
+        <v>0.005813953488372093</v>
       </c>
       <c r="O3">
-        <v>-0.002811244979919678</v>
+        <v>-0.00425531914893617</v>
       </c>
       <c r="P3">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="Q3">
-        <v>0.005223880597014926</v>
+        <v>0.005813953488372093</v>
       </c>
       <c r="R3">
-        <v>-0.002811244979919678</v>
+        <v>-0.00425531914893617</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +743,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.6492537313432836</v>
-      </c>
-      <c r="W3">
-        <v>-0.2721311475409836</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.812851097113492</v>
-      </c>
-      <c r="Y3">
-        <v>-1.084982244654476</v>
-      </c>
-      <c r="Z3">
-        <v>0.3791360294117647</v>
-      </c>
-      <c r="AA3">
-        <v>-0.05468749999999999</v>
+        <v>0.208997860567781</v>
       </c>
       <c r="AB3">
-        <v>0.1202382466294079</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1749257466294079</v>
+        <v>0.208997860567781</v>
       </c>
       <c r="AD3">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>24.36</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.9068797776233496</v>
-      </c>
-      <c r="AI3">
-        <v>0.6726804123711341</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.900887573964497</v>
-      </c>
-      <c r="AK3">
-        <v>0.6573124662709121</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AM3">
-        <v>3.08</v>
+        <v>2.397</v>
       </c>
       <c r="AN3">
-        <v>-37.7713458755427</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-0.7727272727272727</v>
+        <v>-0.5363321799307958</v>
       </c>
       <c r="AP3">
-        <v>-35.25325615050652</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-0.7727272727272727</v>
+        <v>-0.6466416353775553</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_electrical_equipment.xlsx
@@ -587,44 +587,41 @@
           <t>Electrical Equipment</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.127</v>
-      </c>
       <c r="G2">
-        <v>0.005092024539877301</v>
+        <v>0.05932203389830509</v>
       </c>
       <c r="H2">
-        <v>0.005092024539877301</v>
+        <v>0.05932203389830509</v>
       </c>
       <c r="I2">
-        <v>-0.09509202453987729</v>
+        <v>-0.01022598870056497</v>
       </c>
       <c r="J2">
-        <v>-0.09509202453987729</v>
+        <v>-0.01022598870056497</v>
       </c>
       <c r="K2">
-        <v>-2.35</v>
+        <v>-1.87</v>
       </c>
       <c r="L2">
-        <v>-0.1441717791411043</v>
+        <v>-0.1056497175141243</v>
       </c>
       <c r="M2">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="N2">
-        <v>0.005813953488372093</v>
+        <v>0.001910828025477707</v>
       </c>
       <c r="O2">
-        <v>-0.00425531914893617</v>
+        <v>-0.00160427807486631</v>
       </c>
       <c r="P2">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="Q2">
-        <v>0.005813953488372093</v>
+        <v>0.001910828025477707</v>
       </c>
       <c r="R2">
-        <v>-0.00425531914893617</v>
+        <v>-0.00160427807486631</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,52 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.6127388535031847</v>
+      </c>
+      <c r="W2">
+        <v>-0.1558333333333334</v>
       </c>
       <c r="X2">
-        <v>0.208997860567781</v>
+        <v>0.9280227213610663</v>
+      </c>
+      <c r="Y2">
+        <v>-1.0838560546944</v>
+      </c>
+      <c r="Z2">
+        <v>0.4867986798679868</v>
+      </c>
+      <c r="AA2">
+        <v>-0.004977997799779978</v>
       </c>
       <c r="AB2">
-        <v>0.208997860567781</v>
+        <v>0.1938981395182</v>
+      </c>
+      <c r="AC2">
+        <v>-0.19887613731798</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>9.638</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.8709942481511914</v>
+      </c>
+      <c r="AI2">
+        <v>0.7433380084151473</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.8599214846538187</v>
+      </c>
+      <c r="AK2">
+        <v>0.7247706422018348</v>
       </c>
       <c r="AL2">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AM2">
-        <v>2.397</v>
+        <v>2.84</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>15.68047337278106</v>
       </c>
       <c r="AO2">
-        <v>-0.5363321799307958</v>
+        <v>-0.06373239436619718</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>14.25739644970414</v>
       </c>
       <c r="AQ2">
-        <v>-0.6466416353775553</v>
+        <v>-0.06373239436619718</v>
       </c>
     </row>
     <row r="3">
@@ -697,44 +715,41 @@
           <t>Electrical Equipment</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.127</v>
-      </c>
       <c r="G3">
-        <v>0.005092024539877301</v>
+        <v>0.05932203389830509</v>
       </c>
       <c r="H3">
-        <v>0.005092024539877301</v>
+        <v>0.05932203389830509</v>
       </c>
       <c r="I3">
-        <v>-0.09509202453987729</v>
+        <v>-0.01022598870056497</v>
       </c>
       <c r="J3">
-        <v>-0.09509202453987729</v>
+        <v>-0.01022598870056497</v>
       </c>
       <c r="K3">
-        <v>-2.35</v>
+        <v>-1.87</v>
       </c>
       <c r="L3">
-        <v>-0.1441717791411043</v>
+        <v>-0.1056497175141243</v>
       </c>
       <c r="M3">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="N3">
-        <v>0.005813953488372093</v>
+        <v>0.001910828025477707</v>
       </c>
       <c r="O3">
-        <v>-0.00425531914893617</v>
+        <v>-0.00160427807486631</v>
       </c>
       <c r="P3">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="Q3">
-        <v>0.005813953488372093</v>
+        <v>0.001910828025477707</v>
       </c>
       <c r="R3">
-        <v>-0.00425531914893617</v>
+        <v>-0.00160427807486631</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -743,52 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.6127388535031847</v>
+      </c>
+      <c r="W3">
+        <v>-0.1558333333333334</v>
       </c>
       <c r="X3">
-        <v>0.208997860567781</v>
+        <v>0.9280227213610663</v>
+      </c>
+      <c r="Y3">
+        <v>-1.0838560546944</v>
+      </c>
+      <c r="Z3">
+        <v>0.4867986798679868</v>
+      </c>
+      <c r="AA3">
+        <v>-0.004977997799779978</v>
       </c>
       <c r="AB3">
-        <v>0.208997860567781</v>
+        <v>0.1938981395182</v>
+      </c>
+      <c r="AC3">
+        <v>-0.19887613731798</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>9.638</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8709942481511914</v>
+      </c>
+      <c r="AI3">
+        <v>0.7433380084151473</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.8599214846538187</v>
+      </c>
+      <c r="AK3">
+        <v>0.7247706422018348</v>
       </c>
       <c r="AL3">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AM3">
-        <v>2.397</v>
+        <v>2.84</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>15.68047337278106</v>
       </c>
       <c r="AO3">
-        <v>-0.5363321799307958</v>
+        <v>-0.06373239436619718</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>14.25739644970414</v>
       </c>
       <c r="AQ3">
-        <v>-0.6466416353775553</v>
+        <v>-0.06373239436619718</v>
       </c>
     </row>
   </sheetData>
